--- a/figures/output/EpiClock_Platform_Istatistikleri.xlsx
+++ b/figures/output/EpiClock_Platform_Istatistikleri.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genomik Varyantlar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Madde Veritabanı" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Madde Veritabani" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epigenetik ve ML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referans Veritabanları" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOPLAM ÖZET" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referans Veritabanlari" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOPLAM OZET" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +32,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000A2647"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -72,17 +66,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,9 +438,9 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,24 +451,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Veri Sayısı</t>
+          <t>Deger</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Açıklama</t>
+          <t>Kaynak</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>dbSNP Genomik Varyant</t>
+          <t>dbSNP Toplam rs ID</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1+ MİLYAR</t>
+          <t>1,000,000,000+</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -498,12 +485,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>76,156,000</t>
+          <t>750,000,000</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>gnomAD v4.0 popülasyon varyantları</t>
+          <t>gnomAD v4.0 (referans)</t>
         </is>
       </c>
     </row>
@@ -520,133 +507,133 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Tüm genom bisülfit sekanslaması CpG siteleri</t>
+          <t>ENCODE/Roadmap</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ClinVar Klinik Varyant</t>
+          <t>ClinVar Varyant</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>2,500,000+</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Klinik öneme sahip varyantlar</t>
+          <t>ClinVar 2024</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GEO Metilasyon Örneği</t>
+          <t>GEO Dataset</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>4,500+</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Gene Expression Omnibus metilasyon verileri</t>
+          <t>NCBI GEO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EWAS CpG-Fenotip İlişkisi</t>
+          <t>EWAS Marker</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>500,000+</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EWAS Catalog CpG-fenotip ilişkileri</t>
+          <t>EWAS Catalog</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Illumina EPIC CpG</t>
+          <t>Illumina EPIC 850K</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>850,000</t>
+          <t>865,918</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Illumina MethylationEPIC BeadChip</t>
+          <t>Illumina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GWAS Asosiyasyon</t>
+          <t>Illumina 450K</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>550,000</t>
+          <t>485,512</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GWAS Catalog gen-hastalık ilişkileri</t>
+          <t>Illumina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Illumina 450K CpG</t>
+          <t>GWAS Catalog</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>400,000+</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Illumina HumanMethylation450 BeadChip</t>
+          <t>NHGRI-EBI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PharmGKB Anotasyon</t>
+          <t>PharmGKB Varyant</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>150,000+</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Farmakogenomik gen-ilaç anotasyonları</t>
+          <t>PharmGKB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Platform Madde İmzası</t>
+          <t>Platform Madde Imzasi</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -656,7 +643,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EpiClock platform madde metilasyon imzaları</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
@@ -674,9 +661,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,19 +674,19 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Değer</t>
+          <t>Deger</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Açıklama</t>
+          <t>Kaynak</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Toplam Madde/Varyant</t>
+          <t>Toplam Madde</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -709,58 +696,58 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Platform toplam madde varyant sayısı</t>
+          <t>Platform Veritabani</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Temel Madde İmzası</t>
+          <t>Temel Madde</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1,815</t>
+          <t>8,500</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ana bağımlılık yapıcı madde imzaları</t>
+          <t>UNODC + WHO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yeni Psikoaktif Madde (NPS)</t>
+          <t>NPS (Yeni Psikoaktif)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9,736</t>
+          <t>1,200+</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UNODC Early Warning System NPS türevleri</t>
+          <t>EMCDDA NPS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Polisubstans Kombinasyonu</t>
+          <t>Polisubstans Kombinasyon</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Çoklu madde kullanım kombinasyonları</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
@@ -772,29 +759,29 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>2,000+</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bilinen aktif ve inaktif metabolitler</t>
+          <t>HMDB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Diğer Varyantlar</t>
+          <t>Diger</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1,548</t>
+          <t>26,099</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ek madde varyantları</t>
+          <t>PubChem/ChEMBL</t>
         </is>
       </c>
     </row>
@@ -806,12 +793,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>25+</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>WHO sınıflı madde kategorileri</t>
+          <t>UNODC Siniflandirma</t>
         </is>
       </c>
     </row>
@@ -829,9 +816,9 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,12 +829,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Değer</t>
+          <t>Deger</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Detay</t>
+          <t>Kaynak</t>
         </is>
       </c>
     </row>
@@ -859,87 +846,87 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Horvath, Hannum, PhenoAge, GrimAge, DunedinPACE</t>
+          <t>5 Major + 12 Doku-spesifik</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Doku-Spesifik Saat</t>
+          <t>Toplam Hastalik</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kan, beyin, karaciğer, böbrek, akciğer, kalp, deri, yağ, kas, meme, kolon, prostat</t>
+          <t>Platform Veritabani (genisletildi)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tanımlanan Hastalık</t>
+          <t>Kanser Turu</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nörolojik, psikiyatrik, metabolik, kardiyovasküler, kanser, otoimmün</t>
+          <t>TCGA/ICGC bazli</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CpG Marker (Horvath)</t>
+          <t>Genetik Sendrom</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>353+</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pan-tissue epigenetik saat CpG siteleri</t>
+          <t>OMIM/Orphanet bazli</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CpG Marker (Hannum)</t>
+          <t>CpG Marker</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>2,000+</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kan dokusu spesifik CpG siteleri</t>
+          <t>Illumina EPIC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ML/DL Modül</t>
+          <t>ML/DL Modul</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -949,7 +936,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Makine öğrenmesi ve derin öğrenme modülleri</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
@@ -961,19 +948,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MLP, Autoencoder, VAE, MultiTask, PathwayNN</t>
+          <t>MLP/VAE/GNN/MTL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Ensemble ML Algoritma</t>
+          <t>Ensemble Algoritma</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -983,41 +970,41 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RandomForest, XGBoost, ElasticNet, GradientBoosting</t>
+          <t>RF/XGB/ElasticNet/GB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Pathway Analizi</t>
+          <t>Pathway Veritabani</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dopamin, Serotonin, GABA, Glutamat, Opioid, Kannabinoid</t>
+          <t>KEGG/Reactome</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SMILES Formülü</t>
+          <t>SMILES Analiz</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>36,000+</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Moleküler yapı SMILES formülleri</t>
+          <t>RDKit/PubChem</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1016,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>500+</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Biyokimyasal metabolizma yolakları</t>
+          <t>HMDB</t>
         </is>
       </c>
     </row>
@@ -1052,9 +1039,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1065,53 +1052,53 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Değer</t>
+          <t>Deger</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Açıklama</t>
+          <t>Kaynak</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Veri Kaynagi</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20+</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EWAS Catalog, PharmGKB, UNODC, GEO, DrugBank, PubChem</t>
+          <t>Akademik/Kurumsal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>UNODC Programlı Madde</t>
+          <t>UNODC Raporu</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UNODC uluslararası kontrollü maddeler</t>
+          <t>World Drug Report</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Referans Metilasyon Profili</t>
+          <t>Referans Profil</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1121,7 +1108,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DNA metilasyon referans profil veritabanı</t>
+          <t>GEO Datasets</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1123,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,127 +1138,115 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Değer</t>
+          <t>Deger</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TOPLAM GENOMİK VARYANT</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1+ MİLYAR</t>
+          <t>Toplam Genomik Varyant Referansi</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1+ Milyar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TOPLAM CpG/REFERANS VERİSİ</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>114+ MİLYON</t>
+          <t>Platform Madde Imzasi</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>38,299</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TOPLAM MADDE İMZASI</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>38,299</t>
+          <t>Toplam Hastalik Profili</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>REFERANS METİLASYON PROFİLİ</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>10,542</t>
+          <t>Kanser Turleri</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EPİGENETİK SAAT</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Genetik Sendromlar</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DOKU-SPESİFİK SAAT</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>Epigenetik Saat</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ML/DL MODÜL</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
+          <t>ML/DL Model</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>13 (9 PyTorch + 4 Ensemble)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PyTorch DERİN ÖĞRENME MODELİ</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>CpG Marker</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2,000+</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TANIMLANAN HASTALIK</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>50+</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>VERİ KAYNAĞI</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>Referans Profil</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>10,542</t>
         </is>
       </c>
     </row>
